--- a/data/books.xlsx
+++ b/data/books.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Georg\PycharmProjects\BookMoose\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECAB8598-F68F-4796-8756-1346E2F1013A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC1E52F1-DAAB-4C7C-96B2-9DC28A277B44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="33">
   <si>
     <t>title</t>
   </si>
@@ -112,13 +112,25 @@
   </si>
   <si>
     <t>978-517-114463-0</t>
+  </si>
+  <si>
+    <t>copy_id</t>
+  </si>
+  <si>
+    <t>КН001234, КН001235</t>
+  </si>
+  <si>
+    <t>PH001234</t>
+  </si>
+  <si>
+    <t>978-5-17-098659-0-2, 978-5-17-098659-0-1</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -131,6 +143,13 @@
       <color rgb="FF333333"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Consolas"/>
+      <family val="3"/>
       <charset val="204"/>
     </font>
   </fonts>
@@ -154,9 +173,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -437,7 +457,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="17.28515625" customWidth="1"/>
@@ -446,7 +466,7 @@
     <col min="11" max="11" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -480,8 +500,11 @@
       <c r="K1" t="s">
         <v>10</v>
       </c>
+      <c r="L1" s="2" t="s">
+        <v>29</v>
+      </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -510,13 +533,16 @@
         <v>14</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K2">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="L2" t="s">
+        <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -550,8 +576,11 @@
       <c r="K3">
         <v>1</v>
       </c>
+      <c r="L3" t="s">
+        <v>31</v>
+      </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>24</v>
       </c>
@@ -580,10 +609,13 @@
         <v>14</v>
       </c>
       <c r="J4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K4">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="L4" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/data/books.xlsx
+++ b/data/books.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Georg\PycharmProjects\BookMoose\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC1E52F1-DAAB-4C7C-96B2-9DC28A277B44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAAA6276-919F-4ED3-B940-13011751F5DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
